--- a/modelo_aplicacion_medicamento.xlsx
+++ b/modelo_aplicacion_medicamento.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Aplicaciones" sheetId="1" r:id="rId1"/>
     <sheet name="Medicamentos" sheetId="2" r:id="rId2"/>
     <sheet name="Unidades" sheetId="3" r:id="rId3"/>
+    <sheet name="Enfermedades" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -59,6 +60,10 @@
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -80,6 +85,26 @@
       <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Enfermedad</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Sexo (opcional)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Raza (opcional)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Corral (opcional)</t>
         </is>
       </c>
     </row>
@@ -2399,4 +2424,171 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Enfermedad</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Medicamentos del protocolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neumonía</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROFLIN 50ML 2 ml cada 15 kg · subcutáneo · dosis única + FLUMAX 50ml 2 ml cada 45 kg · IM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casco ligera</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MACROSYN 100 ML 1 ml cada 40 kg · IM + AZIUM 10ml 10 ml fijo · IM (o CORTVET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casco severa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MACROSYN 100 ML 1 ml cada 40 kg · subcutáneo + AZIUM 10ml 20 ml fijo · IM (o CORTVET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diarrea</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIO BAC 34G 1 bisnaga · oral · 2 dosis cada 48 h + CLAMOXyL 100ml 1 ml cada 10 kg · IM · 2 dosis cada 48 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Timpanismo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLO-TROL 150ml 75 ml fijo · oral</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tristeza parasitaria</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRAMICINA 50ML 1 ml cada 10 kg · IM + GANASEG 7 30ML 1 ml cada 20 kg · IM + CATOSAL B12 100ml 25 ml fijo · endovenoso o IM + MERCEPTON 100ml 40 ml fijo · IM (o HEPATOXAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesión</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGROVET PLUS 50ml 1 ml cada 20 kg · IM · 2 dosis cada 48 h + FLUMAX 50ml 2 ml cada 45 kg · IM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polioencéfalo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AZIUM 10ml 30 ml fijo · IM (o CORTVET) + MONOVIN B1 20ML 60 ml fijo · IM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intoxicación</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MERCEPTON 100ml 100 ml fijo · IM (o HEPATOXAN) + AZIUM 10ml 20 ml fijo · IM (o CORTVET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requema</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MERCEPTON 100ml 100 ml fijo · IM (o HEPATOXAN) + AZIUM 10ml 20 ml fijo · IM (o CORTVET) + AGROVET PLUS 50ml si hay descamación de la piel: 1 ml cada 20 kg · IM · 2 dosis cada 48 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Queratoconjuntivitis ligera</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRACOTRIL SPRAY spray en el ojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Queratoconjuntivitis severa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRACOTRIL SPRAY spray en el ojo + TERRAMICINA 50ML 1 ml cada 10 kg · IM</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>